--- a/makeList.xlsx
+++ b/makeList.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fivep\OneDrive\Desktop\CLAUDEestimate\auto_make\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="3월 정산" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="4월 정산" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3월 정산'!$A$1:$C$17</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="243">
   <si>
     <t>지점명</t>
   </si>
@@ -549,11 +554,500 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안산롯데마트점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.03.24</t>
+    <t>조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군산롯데마트점</t>
+  </si>
+  <si>
+    <t>호남지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수송점</t>
+  </si>
+  <si>
+    <t>나운점</t>
+  </si>
+  <si>
+    <t>행신역점</t>
+  </si>
+  <si>
+    <t>부평롯데마트점</t>
+  </si>
+  <si>
+    <t>영주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안동옥동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광평점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜관점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우현점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장량점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범서점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동구일산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언양점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>침산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하양점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송현점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽전점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월배점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평리점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>북변점(인)</t>
+  </si>
+  <si>
+    <t>2. 풍무점(인)</t>
+  </si>
+  <si>
+    <t>3. 금촌점(인)</t>
+  </si>
+  <si>
+    <t>4. 운정점(인)</t>
+  </si>
+  <si>
+    <r>
+      <t>8. 오정점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9. 부천중동점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10. 행신영점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11. 부평구청점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12. 화곡점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>13. 작전점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>14. 부평역롯데마트점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 부평롯데마트점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16. 검단점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17. 석남점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인)</t>
+    </r>
+  </si>
+  <si>
+    <t>18. 논현신도시점(인)</t>
+  </si>
+  <si>
+    <t>19. 만수점(인)</t>
+  </si>
+  <si>
+    <t>20. 간석점(인)</t>
+  </si>
+  <si>
+    <t>21. 연수점(인)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>송도롯데마트점(인)</t>
+    </r>
+  </si>
+  <si>
+    <t>북변점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금촌점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운정점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오정점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부천중동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부평구청점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화곡점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작전점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부평역롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검단점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>석남점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현신도시점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만수점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간석점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연수점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송도롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>풍무점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.07</t>
+  </si>
+  <si>
+    <t>2026.04.08</t>
+  </si>
+  <si>
+    <t>2026.04.09</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>비조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.02</t>
+  </si>
+  <si>
+    <t>2026.04.03</t>
+  </si>
+  <si>
+    <t>경북지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강남지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상도점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천호역점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>용인점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수지롯데몰점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분당서현점</t>
+  </si>
+  <si>
+    <t>모란점</t>
+  </si>
+  <si>
+    <t>가락점</t>
+  </si>
+  <si>
+    <t>2026.04.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -564,11 +1058,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +1091,54 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -694,7 +1236,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -702,6 +1244,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -712,6 +1269,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -760,7 +1320,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -795,7 +1355,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1005,14 +1565,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F270"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.19921875" customWidth="1"/>
-    <col min="2" max="2" width="15.296875" customWidth="1"/>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1032,1637 +1592,1718 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>148</v>
+    <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D9" si="0">IF(C2="조명",580000,IF(C2="비조명",290000,0))</f>
-        <v>580000</v>
+        <f t="shared" ref="D2:D22" si="0">IF(C2="조명",580000,IF(C2="비조명",290000,0))</f>
+        <v>290000</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="6">
         <f>SUM(D2:D270)</f>
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>5510000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" t="s">
+        <v>242</v>
+      </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" t="s">
+        <v>242</v>
+      </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" t="s">
+        <v>242</v>
+      </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" t="s">
+        <v>242</v>
+      </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>242</v>
+      </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" t="s">
+        <v>242</v>
+      </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" t="s">
+        <v>242</v>
+      </c>
       <c r="D10">
-        <f>IF(C10="조명",580000,IF(C10="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" t="s">
+        <v>242</v>
+      </c>
       <c r="D11">
-        <f t="shared" ref="D11:D18" si="1">IF(C11="조명",580000,IF(C11="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <f>IF(C23="조명",580000,IF(C23="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <f>IF(C24="조명",580000,IF(C24="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <f>IF(C25="조명",580000,IF(C25="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <f t="shared" ref="D26:D65" si="1">IF(C26="조명",580000,IF(C26="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D13">
+    <row r="28" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D14">
+    <row r="29" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D15">
+    <row r="30" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D16">
+    <row r="31" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D17">
+    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D18">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D19">
-        <f t="shared" ref="D19:D25" si="2">IF(C19="조명",580000,IF(C19="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D26">
-        <f t="shared" ref="D26:D65" si="3">IF(C26="조명",580000,IF(C26="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D27">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D29">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D31">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D32">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D43">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D44">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D45">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D46">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D48">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D50">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D52">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D54">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D56">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D57">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D59">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D60">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D61">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D62">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D63">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D64">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D65">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D66">
-        <f t="shared" ref="D66:D129" si="4">IF(C66="조명",580000,IF(C66="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" ref="D66:D129" si="2">IF(C66="조명",580000,IF(C66="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D67">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D69">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D70">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D71">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D72">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D74">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D76">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D78">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D79">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D80">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D81">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D82">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D83">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D84">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D85">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D86">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D87">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D88">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D89">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D90">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D91">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D92">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D93">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D94">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D95">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D96">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D97">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D98">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D99">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D101">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D103">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D104">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D105">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D106">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D107">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D108">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D109">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D110">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D111">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D112">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D113">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D114">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D115">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D116">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D117">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D118">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D119">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D120">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D121">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D122">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D123">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D124">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D125">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D126">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D127">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D128">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D129">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D130">
-        <f t="shared" ref="D130:D193" si="5">IF(C130="조명",580000,IF(C130="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.4">
+        <f t="shared" ref="D130:D193" si="3">IF(C130="조명",580000,IF(C130="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D131">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D132">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D134">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D135">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D136">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D137">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D138">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D141">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D142">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D143">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D144">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D145">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D146">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D147">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D148">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D149">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D151">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D152">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D153">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D154">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D155">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D156">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D157">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D158">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D159">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D160">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D161">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D162">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D163">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D164">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D165">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D166">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D167">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D168">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D170">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D171">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D172">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D173">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D174">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D175">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D176">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D177">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D178">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D179">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D180">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D181">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D182">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D183">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D184">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D185">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D186">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D187">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D188">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D189">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D190">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D191">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D192">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D193">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D194">
+        <f t="shared" ref="D194:D257" si="4">IF(C194="조명",580000,IF(C194="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D195">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D196">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D197">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D198">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D199">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D201">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D202">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D203">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D204">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D205">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D206">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D207">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D208">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D209">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D210">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D211">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D212">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D213">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D214">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D215">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D216">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D217">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D218">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D219">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D220">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D221">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D222">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D223">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D224">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D225">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D226">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D227">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D228">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D229">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D230">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D231">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D232">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D233">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D234">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D236">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D238">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D239">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D240">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D241">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D242">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D243">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D244">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D245">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D246">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D247">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D248">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D249">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D250">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D251">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D252">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D253">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D254">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D255">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D256">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D257">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D258">
+        <f t="shared" ref="D258:D270" si="5">IF(C258="조명",580000,IF(C258="비조명",290000,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D259">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D132">
+    <row r="260" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D260">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D133">
+    <row r="261" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D261">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D134">
+    <row r="262" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D262">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D135">
+    <row r="263" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D263">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D136">
+    <row r="264" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D264">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D137">
+    <row r="265" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D265">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D138">
+    <row r="266" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D266">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D139">
+    <row r="267" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D267">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D140">
+    <row r="268" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D268">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D141">
+    <row r="269" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D142">
+    <row r="270" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D270">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D143">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D144">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D145">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D146">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D147">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D148">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D149">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D150">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D151">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D152">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D153">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D154">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D155">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D156">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D157">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D158">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D159">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D160">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D161">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D162">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D163">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D164">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D165">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D166">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D167">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D168">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D169">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D170">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D171">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D172">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D173">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D174">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D175">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D176">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D177">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D178">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D179">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D180">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D181">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D182">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D183">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D184">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D185">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D186">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D187">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D188">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D189">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D190">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D191">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D192">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D193">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D194">
-        <f t="shared" ref="D194:D257" si="6">IF(C194="조명",580000,IF(C194="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D195">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D196">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D197">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D198">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D199">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D200">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D201">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D202">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D203">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D204">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D205">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D206">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D207">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D208">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D209">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D210">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D211">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D212">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D213">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D214">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D215">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D216">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D217">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D218">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D219">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D220">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D221">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D222">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D223">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D224">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D225">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D226">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D227">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D228">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D229">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D230">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D231">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D232">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D233">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D234">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D235">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D236">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D237">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D238">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D239">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D240">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D241">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D242">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D243">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D244">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D245">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D246">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D247">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D248">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D249">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D250">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D251">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D252">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D253">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D254">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D255">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D256">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D257">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D258">
-        <f t="shared" ref="D258:D270" si="7">IF(C258="조명",580000,IF(C258="비조명",290000,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D259">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D260">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D261">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D262">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D263">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D264">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D265">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D266">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D267">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D268">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D269">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D270">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2676,19 +3317,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L60"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.69921875" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="6" max="6" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2705,7 +3346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2722,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2739,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2756,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2773,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2790,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2807,7 +3448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2824,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2841,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2858,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2875,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2892,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2909,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2926,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -2943,7 +3584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2960,7 +3601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>144</v>
       </c>
@@ -2977,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -2997,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
         <v>108</v>
       </c>
@@ -3005,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3022,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3039,7 +3680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3056,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3073,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -3090,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3107,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3124,7 +3765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3141,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -3158,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -3175,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F31" t="s">
         <v>118</v>
       </c>
@@ -3183,7 +3824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3200,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F33" t="s">
         <v>52</v>
       </c>
@@ -3208,7 +3849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
         <v>130</v>
       </c>
@@ -3219,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
         <v>131</v>
       </c>
@@ -3230,7 +3871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -3250,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -3270,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -3290,7 +3931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -3310,7 +3951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -3330,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -3350,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -3370,7 +4011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>72</v>
       </c>
@@ -3387,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -3404,7 +4045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
         <v>139</v>
       </c>
@@ -3415,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
         <v>140</v>
       </c>
@@ -3426,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>76</v>
       </c>
@@ -3446,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -3466,7 +4107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -3486,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>123</v>
       </c>
@@ -3503,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>124</v>
       </c>
@@ -3520,7 +4161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -3537,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>126</v>
       </c>
@@ -3557,7 +4198,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F54" t="s">
         <v>79</v>
       </c>
@@ -3568,7 +4209,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F55" t="s">
         <v>125</v>
       </c>
@@ -3579,7 +4220,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F56" t="s">
         <v>126</v>
       </c>
@@ -3590,7 +4231,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -3607,7 +4248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -3624,7 +4265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -3641,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -3668,10 +4309,683 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <dimension ref="A1:AA30"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.75" customWidth="1"/>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="3" max="3" width="26.25" customWidth="1"/>
+    <col min="4" max="4" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" t="s">
+        <v>228</v>
+      </c>
+      <c r="U1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" t="s">
+        <v>216</v>
+      </c>
+      <c r="W1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="U2" t="s">
+        <v>157</v>
+      </c>
+      <c r="V2" t="s">
+        <v>216</v>
+      </c>
+      <c r="W2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="U3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="U4" t="s">
+        <v>159</v>
+      </c>
+      <c r="V4" t="s">
+        <v>217</v>
+      </c>
+      <c r="W4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="U5" t="s">
+        <v>160</v>
+      </c>
+      <c r="V5" t="s">
+        <v>217</v>
+      </c>
+      <c r="W5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="U6" t="s">
+        <v>161</v>
+      </c>
+      <c r="V6" t="s">
+        <v>217</v>
+      </c>
+      <c r="W6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="U7" t="s">
+        <v>162</v>
+      </c>
+      <c r="V7" t="s">
+        <v>217</v>
+      </c>
+      <c r="W7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="U8" t="s">
+        <v>163</v>
+      </c>
+      <c r="V8" t="s">
+        <v>218</v>
+      </c>
+      <c r="W8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="U9" t="s">
+        <v>164</v>
+      </c>
+      <c r="V9" t="s">
+        <v>218</v>
+      </c>
+      <c r="W9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" t="s">
+        <v>238</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="U10" t="s">
+        <v>165</v>
+      </c>
+      <c r="V10" t="s">
+        <v>218</v>
+      </c>
+      <c r="W10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" t="s">
+        <v>239</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="U11" t="s">
+        <v>166</v>
+      </c>
+      <c r="V11" t="s">
+        <v>218</v>
+      </c>
+      <c r="W11" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="R12" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="U12" t="s">
+        <v>172</v>
+      </c>
+      <c r="V12" t="s">
+        <v>219</v>
+      </c>
+      <c r="W12" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="R13" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="U13" t="s">
+        <v>173</v>
+      </c>
+      <c r="V13" t="s">
+        <v>219</v>
+      </c>
+      <c r="W13" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="R14" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="U14" t="s">
+        <v>174</v>
+      </c>
+      <c r="V14" t="s">
+        <v>219</v>
+      </c>
+      <c r="W14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="R15" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="U15" t="s">
+        <v>175</v>
+      </c>
+      <c r="V15" t="s">
+        <v>219</v>
+      </c>
+      <c r="W15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="R16" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="U16" t="s">
+        <v>176</v>
+      </c>
+      <c r="V16" t="s">
+        <v>220</v>
+      </c>
+      <c r="W16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="U17" t="s">
+        <v>177</v>
+      </c>
+      <c r="V17" t="s">
+        <v>220</v>
+      </c>
+      <c r="W17" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="R18" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="U18" t="s">
+        <v>178</v>
+      </c>
+      <c r="V18" t="s">
+        <v>220</v>
+      </c>
+      <c r="W18" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="R19" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="U19" t="s">
+        <v>179</v>
+      </c>
+      <c r="V19" t="s">
+        <v>220</v>
+      </c>
+      <c r="W19" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="R20" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D21" s="7"/>
+      <c r="R21" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D22" s="7"/>
+      <c r="R22" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="D30" s="9"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/makeList.xlsx
+++ b/makeList.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fivep\OneDrive\Desktop\CLAUDEestimate\auto_make\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,12 +14,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3월 정산'!$A$1:$C$17</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="279">
   <si>
     <t>지점명</t>
   </si>
@@ -1054,11 +1049,153 @@
     <t>조명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>미아사거리점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>석관점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공릉점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청구점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중계롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>용두점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍문점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상봉점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥정점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송우점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동두천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덕소롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평내점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진접점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마석점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘천롯데마트점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송정점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양평점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동해점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼척점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태백점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.16</t>
+  </si>
+  <si>
+    <t>2026.04.17</t>
+  </si>
+  <si>
+    <t>조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강북지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -1320,7 +1457,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1355,7 +1492,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1570,6 +1707,7 @@
     <col min="1" max="1" width="19.25" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1593,229 +1731,81 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D22" si="0">IF(C2="조명",580000,IF(C2="비조명",290000,0))</f>
-        <v>290000</v>
-      </c>
       <c r="E2" s="5"/>
       <c r="F2" s="6">
-        <f>SUM(D2:D270)</f>
-        <v>5510000</v>
+        <f>SUM(D17:D270)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f>IF(C14="조명",580000,IF(C14="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D15">
-        <f t="shared" si="0"/>
+        <f>IF(C15="조명",580000,IF(C15="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D16">
-        <f t="shared" si="0"/>
+        <f>IF(C16="조명",580000,IF(C16="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D17">
-        <f t="shared" si="0"/>
+        <f>IF(C17="조명",580000,IF(C17="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D18">
-        <f t="shared" si="0"/>
+        <f>IF(C18="조명",580000,IF(C18="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D19">
-        <f t="shared" si="0"/>
+        <f>IF(C19="조명",580000,IF(C19="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D20">
-        <f t="shared" si="0"/>
+        <f>IF(C20="조명",580000,IF(C20="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D21">
-        <f t="shared" si="0"/>
+        <f>IF(C21="조명",580000,IF(C21="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D22">
-        <f t="shared" si="0"/>
+        <f>IF(C22="조명",580000,IF(C22="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -1839,1471 +1829,1471 @@
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D26">
-        <f t="shared" ref="D26:D65" si="1">IF(C26="조명",580000,IF(C26="비조명",290000,0))</f>
+        <f t="shared" ref="D26:D65" si="0">IF(C26="조명",580000,IF(C26="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D66">
-        <f t="shared" ref="D66:D129" si="2">IF(C66="조명",580000,IF(C66="비조명",290000,0))</f>
+        <f t="shared" ref="D66:D129" si="1">IF(C66="조명",580000,IF(C66="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D103">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D106">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D108">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D111">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D112">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D114">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D115">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D116">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D117">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D118">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D121">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D122">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D123">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D124">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D125">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D126">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D127">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D128">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D130">
-        <f t="shared" ref="D130:D193" si="3">IF(C130="조명",580000,IF(C130="비조명",290000,0))</f>
+        <f t="shared" ref="D130:D193" si="2">IF(C130="조명",580000,IF(C130="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D131">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D132">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D133">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D134">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D136">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D138">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D139">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D140">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D141">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D142">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D143">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D144">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D145">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D146">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D147">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D148">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D150">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D151">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D152">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D153">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D154">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D155">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D157">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D158">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D159">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D161">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D162">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D163">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D164">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D165">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D166">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D167">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D169">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D170">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D171">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D172">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D173">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D175">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D176">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D177">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D178">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D179">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D180">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D181">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D182">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D183">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D185">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D186">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D187">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D188">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D189">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D190">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D191">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D192">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D193">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D194">
-        <f t="shared" ref="D194:D257" si="4">IF(C194="조명",580000,IF(C194="비조명",290000,0))</f>
+        <f t="shared" ref="D194:D257" si="3">IF(C194="조명",580000,IF(C194="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D195">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D196">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D197">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D198">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D199">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D200">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D201">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D202">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D203">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D204">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D205">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D206">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D207">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D208">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D209">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D210">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D211">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D212">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D213">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D214">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D215">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D216">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D217">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D218">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D220">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D221">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D222">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D223">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D224">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D225">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D226">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D227">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D228">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D229">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D230">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D231">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D232">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D233">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D234">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D235">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D236">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D237">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D238">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D239">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D240">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D241">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D242">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D243">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D244">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D245">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D246">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D247">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D248">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D249">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D250">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D251">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D252">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D253">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D254">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D255">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D256">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D257">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D258">
-        <f t="shared" ref="D258:D270" si="5">IF(C258="조명",580000,IF(C258="비조명",290000,0))</f>
+        <f t="shared" ref="D258:D270" si="4">IF(C258="조명",580000,IF(C258="비조명",290000,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D259">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D260">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D261">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D262">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D263">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D265">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D266">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D267">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D268">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D269">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D270">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4309,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
@@ -4317,9 +4307,11 @@
     <col min="3" max="3" width="26.25" customWidth="1"/>
     <col min="4" max="4" width="17.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="28.25" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>150</v>
       </c>
@@ -4335,26 +4327,71 @@
       <c r="E1" t="s">
         <v>228</v>
       </c>
-      <c r="U1" t="s">
+      <c r="F1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1" t="s">
+        <v>276</v>
+      </c>
+      <c r="N1" t="s">
         <v>156</v>
       </c>
-      <c r="V1" t="s">
+      <c r="O1" t="s">
         <v>216</v>
       </c>
+      <c r="P1" t="s">
+        <v>148</v>
+      </c>
+      <c r="R1" t="s">
+        <v>199</v>
+      </c>
+      <c r="S1" t="s">
+        <v>224</v>
+      </c>
+      <c r="T1" t="s">
+        <v>223</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>229</v>
+      </c>
       <c r="W1" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>224</v>
+        <v>240</v>
+      </c>
+      <c r="X1" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y1">
+        <f>IF(X1="조명",580000,IF(X1="비조명",290000,0))</f>
+        <v>290000</v>
       </c>
       <c r="AA1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD1">
+        <f>IF(AC1="조명",580000,IF(AC1="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI1">
+        <f>IF(AH1="조명",580000,IF(AH1="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -4370,29 +4407,74 @@
       <c r="E2" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="F2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" t="s">
+        <v>258</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="U2" t="s">
+      <c r="N2" t="s">
         <v>157</v>
       </c>
-      <c r="V2" t="s">
+      <c r="O2" t="s">
         <v>216</v>
       </c>
+      <c r="P2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" t="s">
+        <v>215</v>
+      </c>
+      <c r="S2" t="s">
+        <v>224</v>
+      </c>
+      <c r="T2" t="s">
+        <v>223</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>231</v>
+      </c>
       <c r="W2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>224</v>
+        <v>240</v>
+      </c>
+      <c r="X2" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y2">
+        <f>IF(X2="조명",580000,IF(X2="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD2">
+        <f>IF(AC2="조명",580000,IF(AC2="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI2">
+        <f>IF(AH2="조명",580000,IF(AH2="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -4408,29 +4490,74 @@
       <c r="E3" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="F3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="U3" t="s">
+      <c r="N3" t="s">
         <v>158</v>
       </c>
-      <c r="V3" t="s">
+      <c r="O3" t="s">
         <v>216</v>
       </c>
+      <c r="P3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" t="s">
+        <v>200</v>
+      </c>
+      <c r="S3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T3" t="s">
+        <v>223</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>232</v>
+      </c>
       <c r="W3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>224</v>
+        <v>240</v>
+      </c>
+      <c r="X3" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y3">
+        <f>IF(X3="조명",580000,IF(X3="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD3">
+        <f>IF(AC3="조명",580000,IF(AC3="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI3">
+        <f>IF(AH3="조명",580000,IF(AH3="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -4446,29 +4573,74 @@
       <c r="E4" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="F4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" t="s">
+        <v>260</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="U4" t="s">
+      <c r="N4" t="s">
         <v>159</v>
       </c>
-      <c r="V4" t="s">
+      <c r="O4" t="s">
         <v>217</v>
       </c>
+      <c r="P4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" t="s">
+        <v>201</v>
+      </c>
+      <c r="S4" t="s">
+        <v>224</v>
+      </c>
+      <c r="T4" t="s">
+        <v>223</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>233</v>
+      </c>
       <c r="W4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>224</v>
+        <v>240</v>
+      </c>
+      <c r="X4" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y4">
+        <f>IF(X4="조명",580000,IF(X4="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD4">
+        <f>IF(AC4="조명",580000,IF(AC4="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>261</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI4">
+        <f>IF(AH4="조명",580000,IF(AH4="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>201</v>
       </c>
@@ -4481,29 +4653,74 @@
       <c r="E5" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="F5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U5" t="s">
+      <c r="N5" t="s">
         <v>160</v>
       </c>
-      <c r="V5" t="s">
+      <c r="O5" t="s">
         <v>217</v>
       </c>
+      <c r="P5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R5" t="s">
+        <v>202</v>
+      </c>
+      <c r="S5" t="s">
+        <v>225</v>
+      </c>
+      <c r="T5" t="s">
+        <v>223</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>234</v>
+      </c>
       <c r="W5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>225</v>
+        <v>240</v>
+      </c>
+      <c r="X5" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y5">
+        <f>IF(X5="조명",580000,IF(X5="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD5">
+        <f>IF(AC5="조명",580000,IF(AC5="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>262</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI5">
+        <f>IF(AH5="조명",580000,IF(AH5="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>202</v>
       </c>
@@ -4514,26 +4731,71 @@
       <c r="E6" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="U6" t="s">
+      <c r="F6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" t="s">
+        <v>262</v>
+      </c>
+      <c r="N6" t="s">
         <v>161</v>
       </c>
-      <c r="V6" t="s">
+      <c r="O6" t="s">
         <v>217</v>
       </c>
+      <c r="P6" t="s">
+        <v>5</v>
+      </c>
+      <c r="R6" t="s">
+        <v>203</v>
+      </c>
+      <c r="S6" t="s">
+        <v>225</v>
+      </c>
+      <c r="T6" t="s">
+        <v>223</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>235</v>
+      </c>
       <c r="W6" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="X6" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y6">
+        <f>IF(X6="조명",580000,IF(X6="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD6">
+        <f>IF(AC6="조명",580000,IF(AC6="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>263</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI6">
+        <f>IF(AH6="조명",580000,IF(AH6="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>203</v>
       </c>
@@ -4544,29 +4806,74 @@
       <c r="E7" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="F7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>263</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="U7" t="s">
+      <c r="N7" t="s">
         <v>162</v>
       </c>
-      <c r="V7" t="s">
+      <c r="O7" t="s">
         <v>217</v>
       </c>
+      <c r="P7" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" t="s">
+        <v>154</v>
+      </c>
+      <c r="S7" t="s">
+        <v>225</v>
+      </c>
+      <c r="T7" t="s">
+        <v>223</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>236</v>
+      </c>
       <c r="W7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="X7" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y7">
+        <f>IF(X7="조명",580000,IF(X7="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD7">
+        <f>IF(AC7="조명",580000,IF(AC7="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>264</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI7">
+        <f>IF(AH7="조명",580000,IF(AH7="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>154</v>
       </c>
@@ -4577,29 +4884,74 @@
       <c r="E8" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="F8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="U8" t="s">
+      <c r="N8" t="s">
         <v>163</v>
       </c>
+      <c r="O8" t="s">
+        <v>218</v>
+      </c>
+      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" t="s">
+        <v>204</v>
+      </c>
+      <c r="S8" t="s">
+        <v>225</v>
+      </c>
+      <c r="T8" t="s">
+        <v>223</v>
+      </c>
       <c r="V8" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="W8" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="X8" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y8">
+        <f>IF(X8="조명",580000,IF(X8="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD8">
+        <f>IF(AC8="조명",580000,IF(AC8="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI8">
+        <f>IF(AH8="조명",580000,IF(AH8="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>204</v>
       </c>
@@ -4610,29 +4962,74 @@
       <c r="E9" t="s">
         <v>237</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="F9" t="s">
+        <v>250</v>
+      </c>
+      <c r="G9" t="s">
+        <v>265</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="U9" t="s">
+      <c r="N9" t="s">
         <v>164</v>
       </c>
+      <c r="O9" t="s">
+        <v>218</v>
+      </c>
+      <c r="P9" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" t="s">
+        <v>205</v>
+      </c>
+      <c r="S9" t="s">
+        <v>225</v>
+      </c>
+      <c r="T9" t="s">
+        <v>223</v>
+      </c>
       <c r="V9" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="W9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="X9" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y9">
+        <f>IF(X9="조명",580000,IF(X9="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA9" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD9">
+        <f>IF(AC9="조명",580000,IF(AC9="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI9">
+        <f>IF(AH9="조명",580000,IF(AH9="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>205</v>
       </c>
@@ -4643,29 +5040,74 @@
       <c r="E10" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="F10" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" t="s">
+        <v>266</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="U10" t="s">
+      <c r="N10" t="s">
         <v>165</v>
       </c>
+      <c r="O10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" t="s">
+        <v>206</v>
+      </c>
+      <c r="S10" t="s">
+        <v>225</v>
+      </c>
+      <c r="T10" t="s">
+        <v>223</v>
+      </c>
       <c r="V10" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="W10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="X10" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y10">
+        <f>IF(X10="조명",580000,IF(X10="비조명",290000,0))</f>
+        <v>580000</v>
       </c>
       <c r="AA10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD10">
+        <f>IF(AC10="조명",580000,IF(AC10="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>267</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI10">
+        <f>IF(AH10="조명",580000,IF(AH10="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>206</v>
       </c>
@@ -4676,29 +5118,61 @@
       <c r="E11" t="s">
         <v>239</v>
       </c>
-      <c r="R11" s="8" t="s">
+      <c r="F11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="U11" t="s">
+      <c r="N11" t="s">
         <v>166</v>
       </c>
-      <c r="V11" t="s">
+      <c r="O11" t="s">
         <v>218</v>
       </c>
-      <c r="W11" t="s">
+      <c r="P11" t="s">
         <v>5</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="R11" t="s">
         <v>207</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="S11" t="s">
         <v>225</v>
       </c>
+      <c r="T11" t="s">
+        <v>223</v>
+      </c>
       <c r="AA11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>272</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD11">
+        <f>IF(AC11="조명",580000,IF(AC11="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>268</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI11">
+        <f>IF(AH11="조명",580000,IF(AH11="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>207</v>
       </c>
@@ -4706,29 +5180,61 @@
         <v>166</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="R12" s="8" t="s">
+      <c r="F12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="U12" t="s">
+      <c r="N12" t="s">
         <v>172</v>
       </c>
-      <c r="V12" t="s">
+      <c r="O12" t="s">
         <v>219</v>
       </c>
-      <c r="W12" t="s">
+      <c r="P12" t="s">
         <v>5</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="R12" t="s">
         <v>155</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="S12" t="s">
         <v>225</v>
       </c>
+      <c r="T12" t="s">
+        <v>223</v>
+      </c>
       <c r="AA12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD12">
+        <f>IF(AC12="조명",580000,IF(AC12="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>269</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI12">
+        <f>IF(AH12="조명",580000,IF(AH12="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>155</v>
       </c>
@@ -4736,29 +5242,48 @@
         <v>172</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="R13" s="8" t="s">
+      <c r="F13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" t="s">
+        <v>269</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="U13" t="s">
+      <c r="N13" t="s">
         <v>173</v>
       </c>
-      <c r="V13" t="s">
+      <c r="O13" t="s">
         <v>219</v>
       </c>
-      <c r="W13" t="s">
+      <c r="P13" t="s">
         <v>222</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="R13" t="s">
         <v>208</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="S13" t="s">
         <v>225</v>
       </c>
+      <c r="T13" t="s">
+        <v>223</v>
+      </c>
       <c r="AA13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD13">
+        <f>IF(AC13="조명",580000,IF(AC13="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>208</v>
       </c>
@@ -4766,29 +5291,45 @@
         <v>173</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="R14" s="8" t="s">
+      <c r="F14" t="s">
+        <v>255</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U14" t="s">
+      <c r="N14" t="s">
         <v>174</v>
       </c>
-      <c r="V14" t="s">
+      <c r="O14" t="s">
         <v>219</v>
       </c>
-      <c r="W14" t="s">
+      <c r="P14" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="R14" t="s">
         <v>209</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="S14" t="s">
         <v>225</v>
       </c>
+      <c r="T14" t="s">
+        <v>223</v>
+      </c>
       <c r="AA14" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD14">
+        <f>IF(AC14="조명",580000,IF(AC14="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>209</v>
       </c>
@@ -4796,29 +5337,45 @@
         <v>174</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="R15" s="8" t="s">
+      <c r="F15" t="s">
+        <v>256</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="U15" t="s">
+      <c r="N15" t="s">
         <v>175</v>
       </c>
-      <c r="V15" t="s">
+      <c r="O15" t="s">
         <v>219</v>
       </c>
-      <c r="W15" t="s">
+      <c r="P15" t="s">
         <v>5</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="R15" t="s">
         <v>210</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="S15" t="s">
         <v>226</v>
       </c>
+      <c r="T15" t="s">
+        <v>223</v>
+      </c>
       <c r="AA15" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>275</v>
+      </c>
+      <c r="AD15">
+        <f>IF(AC15="조명",580000,IF(AC15="비조명",290000,0))</f>
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>210</v>
       </c>
@@ -4826,29 +5383,32 @@
         <v>175</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="R16" s="8" t="s">
+      <c r="F16" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="U16" t="s">
+      <c r="N16" t="s">
         <v>176</v>
       </c>
-      <c r="V16" t="s">
+      <c r="O16" t="s">
         <v>220</v>
       </c>
-      <c r="W16" t="s">
+      <c r="P16" t="s">
         <v>5</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="R16" t="s">
         <v>211</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="S16" t="s">
         <v>226</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="T16" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>211</v>
       </c>
@@ -4856,26 +5416,26 @@
         <v>176</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="U17" t="s">
+      <c r="N17" t="s">
         <v>177</v>
       </c>
-      <c r="V17" t="s">
+      <c r="O17" t="s">
         <v>220</v>
       </c>
-      <c r="W17" t="s">
+      <c r="P17" t="s">
         <v>5</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="R17" t="s">
         <v>212</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="S17" t="s">
         <v>226</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="T17" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>212</v>
       </c>
@@ -4883,29 +5443,29 @@
         <v>177</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="R18" s="7" t="s">
+      <c r="K18" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="U18" t="s">
+      <c r="N18" t="s">
         <v>178</v>
       </c>
-      <c r="V18" t="s">
+      <c r="O18" t="s">
         <v>220</v>
       </c>
-      <c r="W18" t="s">
+      <c r="P18" t="s">
         <v>221</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="R18" t="s">
         <v>213</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="S18" t="s">
         <v>226</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="T18" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>213</v>
       </c>
@@ -4913,29 +5473,29 @@
         <v>178</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="R19" s="9" t="s">
+      <c r="K19" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="U19" t="s">
+      <c r="N19" t="s">
         <v>179</v>
       </c>
-      <c r="V19" t="s">
+      <c r="O19" t="s">
         <v>220</v>
       </c>
-      <c r="W19" t="s">
+      <c r="P19" t="s">
         <v>5</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="R19" t="s">
         <v>214</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="S19" t="s">
         <v>226</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="T19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>214</v>
       </c>
@@ -4943,44 +5503,44 @@
         <v>179</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="R20" s="9" t="s">
+      <c r="K20" s="9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D21" s="7"/>
-      <c r="R21" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D22" s="7"/>
-      <c r="R22" s="10" t="s">
+      <c r="K22" s="10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D24" s="7"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D26" s="7"/>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D28" s="9"/>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D30" s="9"/>
     </row>
   </sheetData>
